--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1351,6 +1351,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7372,7 +7376,7 @@
         <v>422</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>423</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7387,7 +7391,7 @@
         <v>413</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7395,10 +7399,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7424,10 +7428,10 @@
         <v>419</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7478,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7490,7 +7494,7 @@
         <v>422</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>423</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7505,7 +7509,7 @@
         <v>413</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7513,10 +7517,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7542,10 +7546,10 @@
         <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7575,10 +7579,10 @@
         <v>259</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7596,7 +7600,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7623,7 +7627,7 @@
         <v>413</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7631,10 +7635,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7660,16 +7664,16 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7697,10 +7701,10 @@
         <v>248</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7718,7 +7722,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7739,10 +7743,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>352</v>
@@ -7753,10 +7757,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7782,16 +7786,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7819,10 +7823,10 @@
         <v>366</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7840,7 +7844,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7861,10 +7865,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>352</v>
@@ -7875,10 +7879,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7901,17 +7905,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7960,7 +7964,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7987,7 +7991,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7995,10 +7999,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8021,13 +8025,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8078,7 +8082,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8105,7 +8109,7 @@
         <v>413</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8113,10 +8117,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8139,16 +8143,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8198,7 +8202,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8222,7 +8226,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>209</v>
@@ -8233,10 +8237,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8259,16 +8263,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8318,7 +8322,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8342,10 +8346,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8353,10 +8357,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8382,16 +8386,16 @@
         <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8440,7 +8444,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8464,10 +8468,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8475,10 +8479,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8593,10 +8597,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8713,10 +8717,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8835,10 +8839,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8864,13 +8868,13 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>258</v>
@@ -8901,10 +8905,10 @@
         <v>366</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8922,7 +8926,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -8943,7 +8947,7 @@
         <v>263</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>265</v>
@@ -8957,10 +8961,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8983,16 +8987,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>325</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>327</v>
@@ -9044,7 +9048,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9065,7 +9069,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>330</v>
@@ -9079,10 +9083,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9108,13 +9112,13 @@
         <v>243</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>337</v>
@@ -9166,7 +9170,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9201,10 +9205,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9288,7 +9292,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9323,10 +9327,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9352,10 +9356,10 @@
         <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>410</v>
@@ -9410,7 +9414,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fever-observation-profile.xlsx
+++ b/StructureDefinition-fever-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
